--- a/Finance Expenses Data.xlsx
+++ b/Finance Expenses Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itsme\OneDrive\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itsme\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67E2C882-A46C-4A08-AAEE-47E739C3CDE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A990E0A4-1653-4007-9D31-F4A787641BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="4" activeTab="5" xr2:uid="{16A31CDA-A47D-4EBB-BEF8-7F4516B0591E}"/>
   </bookViews>
@@ -2921,6 +2921,365 @@
       <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Pivot!$N$24</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Debit</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Pivot!$M$25:$M$39</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>Clothes</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Coffee</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Doctor</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Donation</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Entertainment</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Furnishings</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Gas/Electrics</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Gifts</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Groceries</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Gym</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>MV Fuel</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Phone</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Rent</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Restaurant</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Taxi</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Pivot!$N$25:$N$39</c:f>
+              <c:numCache>
+                <c:formatCode>_ [$₹-4009]\ * #,##0_ ;_ [$₹-4009]\ * \-#,##0_ ;_ [$₹-4009]\ * "-"??_ ;_ @_ </c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>4690.6000000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1315</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1729</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>620</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3754.6000000000008</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>416.4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>643.70000000000005</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>495.00000000000006</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7464.0999999999995</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1746.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10854</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1527.8999999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>698.20000000000016</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E45C-4E43-8152-2DA065847F50}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="161327584"/>
+        <c:axId val="161328064"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="161327584"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="161328064"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="161328064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_ [$₹-4009]\ * #,##0_ ;_ [$₹-4009]\ * \-#,##0_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="161327584"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[Finance Expenses Data.xlsx]Pivot!PivotTable2</c:name>
     <c:fmtId val="6"/>
@@ -3532,7 +3891,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4072,7 +4431,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4679,7 +5038,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5226,10 +5585,13 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="11">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
   <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
   <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
     <a:lumMod val="60000"/>
@@ -5263,13 +5625,10 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="11">
   <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
   <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
   <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
     <a:lumMod val="60000"/>
@@ -5422,7 +5781,552 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="254">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5936,7 +6840,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="395">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6444,7 +7348,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6949,7 +7853,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7452,7 +8356,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7961,6 +8865,125 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>14111</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>173566</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>141111</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DA344E9-C7D8-3CF9-90A2-90B58454815C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>251178</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>159100</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Month">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92EE6F68-108D-E36C-A1D6-90FAD159D6CC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Month"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5613400" y="3409950"/>
+              <a:ext cx="1828800" cy="2619372"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>225709</xdr:colOff>
       <xdr:row>0</xdr:row>
@@ -8024,7 +9047,10 @@
             <a:rPr lang="en-IN" sz="3800" b="0" cap="none" spc="0">
               <a:ln w="0"/>
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:effectLst>
                 <a:outerShdw blurRad="50800" dist="38100" dir="18900000" algn="bl" rotWithShape="0">
@@ -8042,7 +9068,10 @@
             <a:rPr lang="en-IN" sz="3800" b="0" cap="none" spc="0" baseline="0">
               <a:ln w="0"/>
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:effectLst>
                 <a:outerShdw blurRad="50800" dist="38100" dir="18900000" algn="bl" rotWithShape="0">
@@ -8060,7 +9089,10 @@
             <a:rPr lang="en-IN" sz="3800" b="0" cap="none" spc="0">
               <a:ln w="0"/>
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:effectLst>
                 <a:outerShdw blurRad="50800" dist="38100" dir="18900000" algn="bl" rotWithShape="0">
@@ -18254,6 +19286,12 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Month" xr10:uid="{05DC689A-D026-4C5B-9DAC-0059C463E49F}" cache="Slicer_Month" caption="Month" rowHeight="251883"/>
+</slicers>
+</file>
+
+<file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
   <slicer name="Month 1" xr10:uid="{6DC6E67C-A633-45EA-AF33-5DC7295AE7E9}" cache="Slicer_Month" caption="Month" style="pink1" rowHeight="251883"/>
 </slicers>
 </file>
@@ -38923,6 +39961,14 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId10"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
